--- a/data/trans_orig/IP07_C12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C12_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de cansancio para realizar lo que le gusta en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de haber estado demasiado cansado/a para disfrutar de las cosas que le gusta hacer, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1172,64 +1172,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1515,82 +1515,82 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>988</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>988</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1628,47 +1628,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6219</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,43%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1133</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4432</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10316</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4606</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23849</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33087</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8869</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52814</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>53,49%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79877</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42087</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29834</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48129</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>27637</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8533</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50542</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31755</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51869</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>71789</t>
+          <t>70134</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>58401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97982</t>
+          <t>79124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,74 +2084,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>18,5%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5299</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3800</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6899</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>33,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21086</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>17779</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>22451</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>77,04%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>15210</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>11621</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18319</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>55,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24753</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>39631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -3218,74 +3218,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15905</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>9786</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>56,14%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>54,96%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>49,93%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>18234</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>11329</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>57,36%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -3293,27 +3293,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>4950</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>4910</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>14740</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11287</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>17331</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>72,66%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>55,64%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>85,44%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>12020</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>9264</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>13672</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>81,78%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>63,03%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>93,02%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>30983</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4243,64 +4243,64 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>2,95%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>4566</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>1792</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2950</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>33,06%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>32141</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>35911</t>
+          <t>35114</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>369</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2752</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>801</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13619</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>7097</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>22589</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>5358</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>9614</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>35,22%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>30296</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>21882</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>36751</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>63,7%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>46,01%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>20224</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>15871</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>23605</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>74,1%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>58,15%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>86,48%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>51828</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>39032</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>57052</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,82 +5494,82 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>4683</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>953</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5720,82 +5720,82 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>876</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>4541</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>876</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>15017</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>22732</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>11404</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>7118</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>17547</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>27,63%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>34732</t>
+          <t>37092</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>70403</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>62242</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>76688</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>71,34%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>87,9%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>52100</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>45957</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>56386</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>72,37%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>65492</t>
+          <t>58131</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>51624</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>63050</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>117592</t>
+          <t>128533</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>108460</t>
+          <t>117284</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>124793</t>
+          <t>136379</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>4765</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>47686</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>34801</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>65589</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>58708</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>32701</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>113487</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>53,92%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>106734</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>78553</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>178588</t>
+          <t>105456</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>211560</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>192651</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>225060</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>71,33%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>144753</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>93502</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>170004</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>68,78%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>44,42%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>80,77%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>213317</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>191787</t>
+          <t>143121</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>227517</t>
+          <t>164608</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>358070</t>
+          <t>365627</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>288306</t>
+          <t>343993</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>385157</t>
+          <t>384197</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
